--- a/EstablecimientoSalud/excels/PUNO-PUNO-PUNO.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-PUNO-PUNO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-15.84196861</t>
+          <t>-15.8437211</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-70.02674444</t>
+          <t>-70.0207521</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>POLICLINICO OXIMEDIC  SAC</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "ALFREDO MENDIGURI PINEDA" DE PUNO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HUANCANE NUMERO 324 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>PASAJE RAMIS NUMERO 359 PISO 1 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-15.83309731</t>
+          <t>-15.8402218</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-70.02168738</t>
+          <t>-70.0218805</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CLINICA PROSALUD</t>
+          <t>CENTRO MEDICO AYAVIRI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JR JOSE CARLOS MARIATEGUI 253 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>GRAU NUMERO 354 DISTRITO AYAVIRI PROVINCIA MELGAR DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,22 +642,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.8402218</t>
+          <t>-15.8416987</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-70.0218805</t>
+          <t>-70.0201942</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO CORDOBA EIRL</t>
+          <t>POLICLINICO DE SALUD PNP-PUNO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JR. HUANCANE NÂ° 421 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>AVENIDA AV. JULIACA S/N ALTO HUASCAR NUMERO S/N DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,27 +704,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-15.84198676</t>
+          <t>-15.8451813</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-70.0262981</t>
+          <t>-70.0249132</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SR. DE HUANCA PUNO EIRL</t>
+          <t>PUESTO DE SALUD TACASAYA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AREQUIPA NUMERO 901 PISO 1 URBANIZACION CERCADO DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>CARRETERA CARRETERA PANAMERICANA SUR S/N DISTRITO CHUCUITO NUMERO SIN NUMERO DISTRITO CHUCUITO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,27 +766,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-15.84511926</t>
+          <t>-15.8402218</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-70.02222382</t>
+          <t>-70.0218805</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Consultorio OdontolA³gico MONSSON</t>
+          <t>CENTRO DE ATENCION PRIMARIA III METROPOLITANO DE PUNO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tacna NUMERO 1023 PISO 1 URBANIZACION laykakota DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>JR. AREQUIPA Nº 950 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-15.83852</t>
+          <t>-15.8194556</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-70.02684</t>
+          <t>-70.0387607</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MEDICENTRO TOURISTÂ´S  HEALTH</t>
+          <t>ESTABLECIMIENTO DE SALUD DIVINO NINO JESUS DEL EP-PUNO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jr.MOQUEGUA Nº 191 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>AVENIDA AV TIQUILLACA KM 5 S/N NUMERO S/N DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-15.8485148</t>
+          <t>-15.82486667</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-70.01783241</t>
+          <t>-70.02903167</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO LOS PINOS E.I.R.L.</t>
+          <t>4 DE NOVIEMBRE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PASAJE PASAJE LOS ALAMOS B-2 URBANIZACION LOS PINOS DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>JR. RUBEN DARIO Nº 257 - BARRIO 4 DE NOVIEMBRE DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-15.85801257</t>
+          <t>-15.8215438</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-70.01572751</t>
+          <t>-70.0339387</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SOLIDARIO EL SALVADOR</t>
+          <t>HUERTA HUARAYA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SAN MARTIN NUMERO 343 URBANIZACI? BARRIO SAN MARTIN DE PORRES DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS COMUNIDAD HUERTA HUARAYA DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-15.82459456</t>
+          <t>-15.8417265</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-70.03561341</t>
+          <t>-70.0300675</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CLINICA SANTO DOMINGO</t>
+          <t>SAN JERONIMO DE ULLAGACHI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>YANAMAYO NUMERO 652 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>CARRETERA CAMINO VECINAL DISTRITO VILQUE PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-15.8437211</t>
+          <t>-15.88036833</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-70.0207521</t>
+          <t>-69.9694</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "ALFREDO MENDIGURI PINEDA" DE PUNO</t>
+          <t>JALLIHUAYA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PASAJE RAMIS NUMERO 359 PISO 1 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS CENTRO POBLADO JALLIHUAYA SECTOR INCAPUJIO DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-15.8402218</t>
+          <t>-15.82941167</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-70.0218805</t>
+          <t>-70.020545</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD DE LA EMPRESA DE GENERACION ELECTRICA SAN GABAN S.A.</t>
+          <t>VALLECITO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OTROS CENTRO POBLADO DE CHUANI DISTRITO OLLACHEA PROVINCIA CARABAYA DEPARTAMENTO PUNO</t>
+          <t>OTROS BARRIO VALLECITO DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-15.8402218</t>
+          <t>-15.863885</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-70.0218805</t>
+          <t>-70.00088667</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>POLICLINICO OXIMEDICSAC</t>
+          <t>CHEJONA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SALCEDO NUMERO 190 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>JR. SIDERAL S/N CHEJONA NUMERO S/N DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-15.8471685</t>
+          <t>-15.853201</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.0220062</t>
+          <t>-70.0138529</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO LOS ANGELES MOQUEGUA SAC</t>
+          <t>SAN MARTIN DE PORRES YANICO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MARISACAL NIETO NUMERO 148 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>TROCHA CAMINO VECINAL NUMERO S/N DISTRITO PAUCARCOLLA PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,27 +1324,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-15.8434424</t>
+          <t>-15.8402218</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-70.0275493</t>
+          <t>-70.0218805</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>POLICLINICO OXIMEDIC HEALTH S.A.C.</t>
+          <t>LOS UROS</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LIMA NUMERO 1010 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS ISLA FLOTANTE UROS DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-15.84359772</t>
+          <t>-15.88670333</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-70.02673544</t>
+          <t>-70.00377667</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO CARLOS BARRIQUELO E.I.R.L.</t>
+          <t>SALCEDO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jr.LIMA 1023 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS RINCONADA SALCEDO MANZANA C LOTE 23 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,27 +1448,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-15.841435</t>
+          <t>-15.82896833</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-70.0246513</t>
+          <t>-70.03500167</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO WIAAY</t>
+          <t>VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TACNA NUMERO 976 PISO 1 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS ALTO PUNO DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,27 +1510,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-15.85421858</t>
+          <t>-15.83569</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-70.01622315</t>
+          <t>-70.01544667</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ARCANGEL</t>
+          <t>PUERTO PUNO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4 DE NOVIEMBRE NUMERO 333 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS PUERTO PUNO DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,22 +1572,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-15.8402218</t>
+          <t>-15.84342833</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-70.0218805</t>
+          <t>-70.02131167</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO AYAVIRI</t>
+          <t>METROPOLITANO PUNO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GRAU NUMERO 354 DISTRITO AYAVIRI PROVINCIA MELGAR DEPARTAMENTO PUNO</t>
+          <t>AVENIDA AV. EL SOL Nº 1022 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-15.8470452</t>
+          <t>-15.8579331</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-70.0235465</t>
+          <t>-70.0082584</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ESPECIALIZADO EN GASTROENTEROLOGIA Y ENDOSCOPIA DIGESTIVA "ENDOGASTRO"</t>
+          <t>POLICLANICO MILITAR MANCO CAPAC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PEDRO MIGUEL URBINA 1ER PISO NUMERO 240 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>AVENIDA AV. EL EJARCITO S/N NUMERO S/N DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-15.8416987</t>
+          <t>-15.86454333</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-70.0201942</t>
+          <t>-70.01235833</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>POLICLINICO DE SALUD PNP-PUNO</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AVENIDA AV. JULIACA S/N ALTO HUASCAR NUMERO S/N DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS ASENTAMIENTO HUIMANO SIMON BOLIVAR MANZANA N LOTE 9 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,22 +1758,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-15.8437999</t>
+          <t>-15.83537325</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-70.0271981</t>
+          <t>-70.01481556</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>policlinico virgen de guadalupe puno EIRL</t>
+          <t>PIAS LAGO TITICACA I</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>salcedo NUMERO 270 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS MUELLE DEL LAGO TITICACA NUMERO S/N DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-15.8402218</t>
+          <t>-15.96015167</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-70.0218805</t>
+          <t>-69.99090667</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CLINICA LAS KALAS</t>
+          <t>COLLACACHI</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TACNA NUMERO 890 PISO 6 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS CENTRO POBLADO COLLACACHI DISTRITO PICHACANI PROVINCIA PUNO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25660</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CENTRO ESPECIALIZADO EN SALUD SEXUAL Y REPRODUCTIVA MADAME FESSEL</t>
+          <t>ENFERMERIA DE LA ESCUELA DE MONTANA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MOQUEGUA NUMERO 618 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>OTROS CENTRO POBLADO SANTA ROSA S/N, FUERTE MARISCAL CACERES S/N CENTRO POBLADO SANTA ROSA S/N, FUERTE MARISCAL CACERES SANTA ROSA EL COLLAO PUNO</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26095</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1944,22 +1944,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-15.83722425</t>
+          <t>-15.8376089</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-70.02695537</t>
+          <t>-70.0194325</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLOGICO NEWDENT</t>
+          <t>CHOCOCONIRI</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Teodoro Valcarcel NUMERO 187 PISO 2 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
+          <t>TROCHA CARROZABLE COMUNIDAD DE CHOCOCONIRI DISTRITO JULI PROVINCIA CHUCUITO DEPARTAMENTO PUNO</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1973,750 +1973,6 @@
         </is>
       </c>
       <c r="L25" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>26226</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-15.8402218</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-70.0218805</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ODONTOLOGICO ORAL SUR</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>TACNA NUMERO 281 PISO 2 DEPARTAMENTO 202 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>35159</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-15.8402218</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-70.0218805</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>CLINICA SANTO REMEDIO</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>RICARDO PALMA NUMERO 214 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>I-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-15.8360856</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-70.0302132</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>CLINICA ESPECIALIZADA DENTAL MERCADO ODONTOLOGIA DE ALTA CALIDAD E.I.R.L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>PARDO NUMERO 511 PISO 2 URBANIZACION AZOGUINI DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>25265</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-15.84040242</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-70.02546393</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO SAN REMO</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>TACNA NUMERO 562 PISO 1 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>27066</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-15.83249632</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-70.02464395</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO MEDIDENT PUNO</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>AVENIDA FLORAL NUMERO 375 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>26528</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-15.84132619</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-70.02567314</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO VIRGEN DEL CARMEN SRL.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>MOQUEGUA NUMERO 571 PISO 1 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>30879</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-15.84197293</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-70.02726729</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO CARLOS BARRIQUELO</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>LIMA NUMERO 854 PISO 2 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>36236</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-15.84121265</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-70.02342545</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>CENTRO DE GINECOLOGIA INTEGRAL</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>TACNA NUMERO 905 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>10379</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-15.8410613</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-70.0301656</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>CENTRO  ODONTOLOGICO AMERICANO - PUNO</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Jr.DEUSTUA 754 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>24362</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-15.8451813</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-70.0249132</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD TACASAYA</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>CARRETERA CARRETERA PANAMERICANA SUR S/N DISTRITO CHUCUITO NUMERO SIN NUMERO DISTRITO CHUCUITO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>26343</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-15.84572389</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-70.02192355</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>CENTRO ODONTOLOGIGO "SARVEL"</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Tacna NUMERO 1085 PISO 1 URBANIZACI? La Victoria DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>9217</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-15.8402218</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-70.0218805</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>CENTRO DE ATENCION PRIMARIA III METROPOLITANO DE PUNO</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>JR. AREQUIPA Nº 950 DISTRITO PUNO PROVINCIA PUNO DEPARTAMENTO PUNO</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
         <is>
           <t>210101</t>
         </is>

--- a/EstablecimientoSalud/excels/PUNO-PUNO-PUNO.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-PUNO-PUNO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>29833</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-15.8437211</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>29680</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-15.8402218</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>10235</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-15.8416987</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>24362</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-15.8451813</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>9217</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-15.8402218</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>18948</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-15.8194556</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>3252</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-15.82486667</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>3258</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-15.8215438</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>25806</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-15.8417265</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>3260</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-15.88036833</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>3255</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-15.82941167</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>3253</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-15.863885</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>24200</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-15.853201</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>3261</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-15.8402218</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>3264</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-15.88670333</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>3266</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-15.82896833</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>3263</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-15.83569</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-15.84342833</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>21066</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-15.8579331</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>3265</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-15.86454333</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>24337</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-15.83537325</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>3268</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-15.96015167</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>10882</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-15.8402218</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>30968</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>210101</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-15.8376089</t>
@@ -1970,11 +1850,6 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>210101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/PUNO-PUNO-PUNO.xlsx
+++ b/EstablecimientoSalud/excels/PUNO-PUNO-PUNO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
